--- a/proteomics.xlsx
+++ b/proteomics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/kiarish_cop_sc_edu/Documents/Tuyen/IS-bonding studies/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/huynhdam_email_sc_edu/Documents/Documents/GitHub/Bonding_studies/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_F25DC773A252ABDACC1048BC0118678E5ADE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A25090B8-F7F7-4B51-9704-E054CEC345B6}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_F25DC773A252ABDACC1048BC0118678E5ADE58F7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF8F8A07-7A07-5A3E-B5F9-5460C73AABE5}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2175" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
